--- a/data/trans_orig/PCS12_SP_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/PCS12_SP_R2-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12) en 2007</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>106015</t>
+          <t>106042</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>138869</t>
+          <t>138826</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>131518</t>
+          <t>132451</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>165242</t>
+          <t>164675</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>249366</t>
+          <t>246697</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>298082</t>
+          <t>294011</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,07%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>134141</t>
+          <t>134184</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>166995</t>
+          <t>166968</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95596</t>
+          <t>96163</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>129320</t>
+          <t>128387</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>235766</t>
+          <t>239837</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>284482</t>
+          <t>287151</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,79%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>218900</t>
+          <t>214727</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>264248</t>
+          <t>262900</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>273009</t>
+          <t>275968</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>318640</t>
+          <t>319840</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>503075</t>
+          <t>504944</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>566982</t>
+          <t>569597</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>57,13%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>228827</t>
+          <t>230175</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>274175</t>
+          <t>278348</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>185309</t>
+          <t>184109</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>230940</t>
+          <t>227981</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>430042</t>
+          <t>427427</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>493949</t>
+          <t>492080</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,35%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>118475</t>
+          <t>117361</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>153410</t>
+          <t>152885</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>215242</t>
+          <t>214974</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>248492</t>
+          <t>248616</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>341748</t>
+          <t>341496</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>392507</t>
+          <t>392611</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,01%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>165436</t>
+          <t>165961</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>200371</t>
+          <t>201485</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86920</t>
+          <t>86796</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>120170</t>
+          <t>120438</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>261751</t>
+          <t>261647</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>312510</t>
+          <t>312762</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,8%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>129475</t>
+          <t>129183</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>165603</t>
+          <t>164523</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>206205</t>
+          <t>206454</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>243127</t>
+          <t>240969</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>347881</t>
+          <t>343754</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>402560</t>
+          <t>397841</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>54,49%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>193068</t>
+          <t>194148</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>229196</t>
+          <t>229488</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>128329</t>
+          <t>130487</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>165251</t>
+          <t>165002</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>327567</t>
+          <t>332286</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>382246</t>
+          <t>386373</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,92%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56997</t>
+          <t>56116</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83366</t>
+          <t>83228</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>86294</t>
+          <t>88564</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>115218</t>
+          <t>118427</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>150787</t>
+          <t>150984</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>190519</t>
+          <t>189827</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,19%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>119942</t>
+          <t>120080</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>146311</t>
+          <t>147192</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>92450</t>
+          <t>89241</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>121374</t>
+          <t>119104</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>220457</t>
+          <t>221149</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>260189</t>
+          <t>259992</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,26%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>100415</t>
+          <t>100985</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>132041</t>
+          <t>133584</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>175392</t>
+          <t>174890</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>206086</t>
+          <t>205251</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>285478</t>
+          <t>283971</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>329697</t>
+          <t>332294</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,53%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>138770</t>
+          <t>137227</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>170396</t>
+          <t>169826</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>72058</t>
+          <t>72893</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>102752</t>
+          <t>103254</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>219258</t>
+          <t>216661</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>263477</t>
+          <t>264984</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>48,27%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>255972</t>
+          <t>257425</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>309330</t>
+          <t>306780</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>341002</t>
+          <t>340319</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>391247</t>
+          <t>390800</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>607787</t>
+          <t>610493</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>682840</t>
+          <t>685035</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,66%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>305697</t>
+          <t>308247</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>359055</t>
+          <t>357602</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>246972</t>
+          <t>247419</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>297217</t>
+          <t>297900</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>570406</t>
+          <t>568211</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>645459</t>
+          <t>642753</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,29%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>258063</t>
+          <t>257197</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>313824</t>
+          <t>314474</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>341954</t>
+          <t>339401</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>396812</t>
+          <t>395676</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>613690</t>
+          <t>614246</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>689956</t>
+          <t>691914</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,3%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>429971</t>
+          <t>429321</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>485732</t>
+          <t>486598</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>386699</t>
+          <t>387835</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>441557</t>
+          <t>444110</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>837350</t>
+          <t>835392</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>913616</t>
+          <t>913060</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,78%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1342788</t>
+          <t>1334686</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1458215</t>
+          <t>1458948</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1870650</t>
+          <t>1865497</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1988583</t>
+          <t>1982855</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3234788</t>
+          <t>3242413</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3405160</t>
+          <t>3406066</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,17%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1818328</t>
+          <t>1817595</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1933755</t>
+          <t>1941857</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1390614</t>
+          <t>1396342</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1508547</t>
+          <t>1513700</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3250581</t>
+          <t>3249675</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3420953</t>
+          <t>3413328</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,28%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12) en 2012</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>132343</t>
+          <t>132875</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>168657</t>
+          <t>166591</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>141418</t>
+          <t>141082</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>177060</t>
+          <t>176719</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>284996</t>
+          <t>284353</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>333385</t>
+          <t>336112</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,75%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>126081</t>
+          <t>128147</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>162395</t>
+          <t>161863</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>110185</t>
+          <t>110526</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>145827</t>
+          <t>146163</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>248598</t>
+          <t>245871</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>296987</t>
+          <t>297630</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,14%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>231836</t>
+          <t>234172</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>280027</t>
+          <t>280899</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>312805</t>
+          <t>311736</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>355335</t>
+          <t>354418</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>555594</t>
+          <t>554677</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>623189</t>
+          <t>620159</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,25%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>225500</t>
+          <t>224628</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>273691</t>
+          <t>271355</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>168430</t>
+          <t>169347</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>210960</t>
+          <t>212029</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>406103</t>
+          <t>409133</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>473698</t>
+          <t>474615</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>46,11%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>119847</t>
+          <t>117920</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155499</t>
+          <t>155539</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>160320</t>
+          <t>161382</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>198549</t>
+          <t>198160</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>290642</t>
+          <t>291242</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>342419</t>
+          <t>344177</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>168547</t>
+          <t>168507</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>204199</t>
+          <t>206126</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142471</t>
+          <t>142860</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>180700</t>
+          <t>179638</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>322647</t>
+          <t>320889</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>374424</t>
+          <t>373824</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,21%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>119876</t>
+          <t>120591</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>159897</t>
+          <t>159332</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>176887</t>
+          <t>178654</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>216820</t>
+          <t>217556</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>309450</t>
+          <t>308753</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>366413</t>
+          <t>365954</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>47,97%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>214085</t>
+          <t>214650</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>254106</t>
+          <t>253391</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>172131</t>
+          <t>171395</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>212064</t>
+          <t>210297</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>396520</t>
+          <t>396979</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>453483</t>
+          <t>454180</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,53%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>79790</t>
+          <t>78960</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>109856</t>
+          <t>110530</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>111693</t>
+          <t>112510</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142043</t>
+          <t>142761</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>202487</t>
+          <t>200845</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>243624</t>
+          <t>243878</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,43%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>102762</t>
+          <t>102088</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>132828</t>
+          <t>133658</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>77548</t>
+          <t>76830</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>107898</t>
+          <t>107081</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>188585</t>
+          <t>188331</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>229722</t>
+          <t>231364</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>53,53%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>113783</t>
+          <t>112800</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>147978</t>
+          <t>146889</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>138583</t>
+          <t>139741</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>172074</t>
+          <t>173813</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>260095</t>
+          <t>261840</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>309974</t>
+          <t>309788</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,92%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>126003</t>
+          <t>127092</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>160198</t>
+          <t>161181</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>107957</t>
+          <t>106218</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>141448</t>
+          <t>140290</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>244038</t>
+          <t>244224</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>293917</t>
+          <t>292172</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>52,74%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>249402</t>
+          <t>248911</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>301679</t>
+          <t>303875</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>337012</t>
+          <t>343014</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>394912</t>
+          <t>395444</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>605749</t>
+          <t>607412</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>682125</t>
+          <t>681297</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,22%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>361109</t>
+          <t>358913</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>413386</t>
+          <t>413877</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>298941</t>
+          <t>298409</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>356841</t>
+          <t>350839</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>674516</t>
+          <t>675344</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>750892</t>
+          <t>749229</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,23%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>296407</t>
+          <t>294183</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>353156</t>
+          <t>352342</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>380061</t>
+          <t>378048</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>440156</t>
+          <t>437205</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>691466</t>
+          <t>691057</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>777035</t>
+          <t>780360</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,68%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>425942</t>
+          <t>426756</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>482691</t>
+          <t>484915</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>383697</t>
+          <t>386648</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>443792</t>
+          <t>445805</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>825916</t>
+          <t>822591</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>911485</t>
+          <t>911894</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,89%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1445255</t>
+          <t>1454404</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1572564</t>
+          <t>1573064</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1871924</t>
+          <t>1874277</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2000271</t>
+          <t>1994639</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3353430</t>
+          <t>3351809</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3524304</t>
+          <t>3525395</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,47%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1854215</t>
+          <t>1853715</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1981524</t>
+          <t>1972375</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1558038</t>
+          <t>1563670</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1686385</t>
+          <t>1684032</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3460784</t>
+          <t>3459693</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3631658</t>
+          <t>3633279</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,01%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12) en 2016</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>114726</t>
+          <t>117372</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>150398</t>
+          <t>152678</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>139900</t>
+          <t>140153</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>175713</t>
+          <t>174011</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>266461</t>
+          <t>263786</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>315937</t>
+          <t>316316</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,31%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>143363</t>
+          <t>141083</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>179035</t>
+          <t>176389</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>112990</t>
+          <t>114692</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>148803</t>
+          <t>148550</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>266527</t>
+          <t>266148</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>316003</t>
+          <t>318678</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,71%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>205275</t>
+          <t>204083</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>249418</t>
+          <t>251240</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>253415</t>
+          <t>256773</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>302349</t>
+          <t>300761</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>470043</t>
+          <t>472117</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>535026</t>
+          <t>538575</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,51%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>253157</t>
+          <t>251335</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>297300</t>
+          <t>298492</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>220735</t>
+          <t>222323</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>269669</t>
+          <t>266311</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>490633</t>
+          <t>487084</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>555616</t>
+          <t>553542</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>53,97%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81050</t>
+          <t>80965</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>113216</t>
+          <t>111402</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94395</t>
+          <t>97332</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130230</t>
+          <t>131807</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>188532</t>
+          <t>184480</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>233629</t>
+          <t>231817</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,4%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>205349</t>
+          <t>207163</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>237515</t>
+          <t>237600</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>206079</t>
+          <t>204502</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>241914</t>
+          <t>238977</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>421245</t>
+          <t>423057</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>466342</t>
+          <t>470394</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,83%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>186141</t>
+          <t>187181</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>225114</t>
+          <t>227146</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>226466</t>
+          <t>225413</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>266172</t>
+          <t>266683</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>426872</t>
+          <t>424298</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>481310</t>
+          <t>479978</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,38%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>144850</t>
+          <t>142818</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>183823</t>
+          <t>182783</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121111</t>
+          <t>120600</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>160817</t>
+          <t>161870</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>275937</t>
+          <t>277269</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>330375</t>
+          <t>332949</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,97%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51334</t>
+          <t>52875</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78878</t>
+          <t>79877</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72028</t>
+          <t>71608</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>100184</t>
+          <t>101500</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>132011</t>
+          <t>132118</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>170119</t>
+          <t>170545</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,68%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>132343</t>
+          <t>131344</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>159887</t>
+          <t>158346</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>118403</t>
+          <t>117087</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>146559</t>
+          <t>146979</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>259689</t>
+          <t>259263</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>297797</t>
+          <t>297690</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,26%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77444</t>
+          <t>76717</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>106535</t>
+          <t>107672</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>106526</t>
+          <t>108264</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>139730</t>
+          <t>140916</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>193659</t>
+          <t>193816</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>240353</t>
+          <t>241443</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>45,03%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>156588</t>
+          <t>155451</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>185679</t>
+          <t>186406</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>133385</t>
+          <t>132199</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>166589</t>
+          <t>164851</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>295885</t>
+          <t>294795</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>342579</t>
+          <t>342422</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,86%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>224020</t>
+          <t>227260</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>278221</t>
+          <t>276781</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>314958</t>
+          <t>314631</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>366399</t>
+          <t>365758</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>557196</t>
+          <t>559045</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>633428</t>
+          <t>635211</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,13%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>378337</t>
+          <t>379777</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>432538</t>
+          <t>429298</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>324895</t>
+          <t>325536</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>376336</t>
+          <t>376663</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>714424</t>
+          <t>712641</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>790656</t>
+          <t>788807</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,52%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>222168</t>
+          <t>225099</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>275323</t>
+          <t>275246</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>319333</t>
+          <t>322558</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>378052</t>
+          <t>380309</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>555786</t>
+          <t>558082</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>637914</t>
+          <t>639015</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,82%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>503260</t>
+          <t>503337</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>556415</t>
+          <t>553484</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>448115</t>
+          <t>445858</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>506834</t>
+          <t>503609</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>966836</t>
+          <t>965735</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1048964</t>
+          <t>1046668</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,22%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1270293</t>
+          <t>1265887</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1381491</t>
+          <t>1383208</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1629512</t>
+          <t>1638475</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1758713</t>
+          <t>1758059</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2930007</t>
+          <t>2927561</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3097352</t>
+          <t>3102177</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2012859</t>
+          <t>2011142</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2124057</t>
+          <t>2128463</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1785829</t>
+          <t>1786483</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1915030</t>
+          <t>1906067</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3841540</t>
+          <t>3836715</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4008885</t>
+          <t>4011331</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,81%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12) en 2023</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) en 2023 (tasa de respuesta: 99,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>163677</t>
+          <t>165620</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>209539</t>
+          <t>209758</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>216113</t>
+          <t>218191</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>241252</t>
+          <t>242760</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>391564</t>
+          <t>389221</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>445948</t>
+          <t>444879</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,01%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101904</t>
+          <t>101685</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>147766</t>
+          <t>145823</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48383</t>
+          <t>46875</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73522</t>
+          <t>71444</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>155129</t>
+          <t>156198</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>209513</t>
+          <t>211856</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,25%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>202924</t>
+          <t>202796</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>263575</t>
+          <t>259856</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>266471</t>
+          <t>268097</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>308593</t>
+          <t>305853</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>486688</t>
+          <t>480363</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>557417</t>
+          <t>551589</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>53,5%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>253944</t>
+          <t>257663</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>314595</t>
+          <t>314723</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>204984</t>
+          <t>207724</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>247106</t>
+          <t>245480</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>473679</t>
+          <t>479507</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>544408</t>
+          <t>550733</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>53,41%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>146315</t>
+          <t>146549</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>183177</t>
+          <t>182277</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>163620</t>
+          <t>162150</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>193800</t>
+          <t>195687</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>319092</t>
+          <t>318851</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>367864</t>
+          <t>367790</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,88%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>130900</t>
+          <t>131800</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>167762</t>
+          <t>167528</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150305</t>
+          <t>148418</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>180485</t>
+          <t>181955</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>290318</t>
+          <t>290392</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>339090</t>
+          <t>339331</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,56%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>127666</t>
+          <t>128819</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>175525</t>
+          <t>171910</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>123595</t>
+          <t>117621</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>246813</t>
+          <t>251654</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>252782</t>
+          <t>241723</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>403416</t>
+          <t>400160</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,52%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>130659</t>
+          <t>134274</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>178518</t>
+          <t>177365</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>223666</t>
+          <t>218825</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>346884</t>
+          <t>352858</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>373247</t>
+          <t>376503</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>523881</t>
+          <t>534940</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>68,88%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63711</t>
+          <t>64104</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86038</t>
+          <t>85435</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99413</t>
+          <t>98774</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119471</t>
+          <t>119330</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>168606</t>
+          <t>168884</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>200158</t>
+          <t>197946</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>51,43%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92201</t>
+          <t>92804</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114528</t>
+          <t>114135</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87176</t>
+          <t>87317</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>107234</t>
+          <t>107873</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>184728</t>
+          <t>186940</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>216280</t>
+          <t>216002</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>56,12%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>132798</t>
+          <t>133176</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>162887</t>
+          <t>163608</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>147029</t>
+          <t>147027</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>172086</t>
+          <t>172960</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>287093</t>
+          <t>286837</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>327854</t>
+          <t>326090</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>61,97%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>106277</t>
+          <t>105556</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>136366</t>
+          <t>135988</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>84970</t>
+          <t>84096</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>110027</t>
+          <t>110029</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>198366</t>
+          <t>200130</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>239127</t>
+          <t>239383</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,49%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>265471</t>
+          <t>267566</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>326491</t>
+          <t>327210</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>426634</t>
+          <t>429115</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>716421</t>
+          <t>698925</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>721843</t>
+          <t>716268</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1106900</t>
+          <t>1101041</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>293410</t>
+          <t>292691</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>354430</t>
+          <t>352335</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>130443</t>
+          <t>147939</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>420230</t>
+          <t>417749</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>359865</t>
+          <t>365724</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>744922</t>
+          <t>750497</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>51,17%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>280887</t>
+          <t>281912</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>715435</t>
+          <t>712108</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>271563</t>
+          <t>268889</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>316113</t>
+          <t>314109</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>584051</t>
+          <t>584079</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1094590</t>
+          <t>1123850</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>68,43%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>211749</t>
+          <t>215076</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>646297</t>
+          <t>645272</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>399128</t>
+          <t>401132</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>443678</t>
+          <t>446352</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>547835</t>
+          <t>518575</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1058374</t>
+          <t>1058346</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1557120</t>
+          <t>1563703</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2116180</t>
+          <t>2095632</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1855580</t>
+          <t>1855890</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2301535</t>
+          <t>2301980</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3473685</t>
+          <t>3474211</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4140835</t>
+          <t>4180808</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,99%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1327531</t>
+          <t>1348079</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1886591</t>
+          <t>1880008</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1342068</t>
+          <t>1341623</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1788023</t>
+          <t>1787713</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2946479</t>
+          <t>2906506</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3613629</t>
+          <t>3613103</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/PCS12_SP_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/PCS12_SP_R2-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>106042</t>
+          <t>106991</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>138826</t>
+          <t>139227</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>132451</t>
+          <t>130452</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>164675</t>
+          <t>163527</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>246697</t>
+          <t>247016</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>294011</t>
+          <t>292980</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,88%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>134184</t>
+          <t>133783</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>166968</t>
+          <t>166019</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>96163</t>
+          <t>97311</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128387</t>
+          <t>130386</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>239837</t>
+          <t>240868</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>287151</t>
+          <t>286832</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,73%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>214727</t>
+          <t>216828</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>262900</t>
+          <t>260604</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>275968</t>
+          <t>274764</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>319840</t>
+          <t>317410</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>504944</t>
+          <t>505908</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>569597</t>
+          <t>568608</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>57,03%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>230175</t>
+          <t>232471</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>278348</t>
+          <t>276247</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>184109</t>
+          <t>186539</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>227981</t>
+          <t>229185</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>427427</t>
+          <t>428416</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>492080</t>
+          <t>491116</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,26%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>117361</t>
+          <t>115684</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>152885</t>
+          <t>152212</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>214974</t>
+          <t>213681</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>248616</t>
+          <t>247483</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>341496</t>
+          <t>340894</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>392611</t>
+          <t>392093</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>59,93%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>165961</t>
+          <t>166634</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>201485</t>
+          <t>203162</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86796</t>
+          <t>87929</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>120438</t>
+          <t>121731</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>261647</t>
+          <t>262165</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>312762</t>
+          <t>313364</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,9%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>129183</t>
+          <t>129084</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>164523</t>
+          <t>166027</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>206454</t>
+          <t>205925</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>240969</t>
+          <t>243199</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>343754</t>
+          <t>345306</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>397841</t>
+          <t>399259</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,68%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>194148</t>
+          <t>192644</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>229488</t>
+          <t>229587</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>130487</t>
+          <t>128257</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>165002</t>
+          <t>165531</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>332286</t>
+          <t>330868</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>386373</t>
+          <t>384821</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,71%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56116</t>
+          <t>56020</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83228</t>
+          <t>83424</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>88564</t>
+          <t>86325</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>118427</t>
+          <t>116663</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>150984</t>
+          <t>149829</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>189827</t>
+          <t>192286</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,79%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>120080</t>
+          <t>119884</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>147192</t>
+          <t>147288</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89241</t>
+          <t>91005</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>119104</t>
+          <t>121343</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>221149</t>
+          <t>218690</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>259992</t>
+          <t>261147</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,54%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>100985</t>
+          <t>101207</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>133584</t>
+          <t>133401</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>174890</t>
+          <t>176672</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>205251</t>
+          <t>206055</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>283971</t>
+          <t>285886</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>332294</t>
+          <t>332466</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,56%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>137227</t>
+          <t>137410</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>169826</t>
+          <t>169604</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>72893</t>
+          <t>72089</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>103254</t>
+          <t>101472</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>216661</t>
+          <t>216489</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>264984</t>
+          <t>263069</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>47,92%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>257425</t>
+          <t>255391</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>306780</t>
+          <t>306181</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>340319</t>
+          <t>337929</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>390800</t>
+          <t>392597</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>610493</t>
+          <t>610844</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>685035</t>
+          <t>678692</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,15%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>308247</t>
+          <t>308846</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>357602</t>
+          <t>359636</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>247419</t>
+          <t>245622</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>297900</t>
+          <t>300290</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>568211</t>
+          <t>574554</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>642753</t>
+          <t>642402</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,26%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>257197</t>
+          <t>257183</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>314474</t>
+          <t>313105</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>339401</t>
+          <t>340189</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>395676</t>
+          <t>398472</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>614246</t>
+          <t>614349</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>691914</t>
+          <t>694816</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,49%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>429321</t>
+          <t>430690</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>486598</t>
+          <t>486612</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>387835</t>
+          <t>385039</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>444110</t>
+          <t>443322</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>835392</t>
+          <t>832490</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>913060</t>
+          <t>912957</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1334686</t>
+          <t>1334087</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1458948</t>
+          <t>1455877</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1865497</t>
+          <t>1867507</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1982855</t>
+          <t>1984856</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3242413</t>
+          <t>3242541</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3406066</t>
+          <t>3411872</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,26%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1817595</t>
+          <t>1820666</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1941857</t>
+          <t>1942456</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1396342</t>
+          <t>1394341</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1513700</t>
+          <t>1511690</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3249675</t>
+          <t>3243869</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3413328</t>
+          <t>3413200</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>132875</t>
+          <t>131932</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>166591</t>
+          <t>167800</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>141082</t>
+          <t>142525</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>176719</t>
+          <t>177764</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>284353</t>
+          <t>285119</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>336112</t>
+          <t>334302</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,44%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>128147</t>
+          <t>126938</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>161863</t>
+          <t>162806</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>110526</t>
+          <t>109481</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>146163</t>
+          <t>144720</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>245871</t>
+          <t>247681</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>297630</t>
+          <t>296864</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,01%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>234172</t>
+          <t>232523</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>280899</t>
+          <t>279058</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>311409</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>354418</t>
+          <t>357325</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>554677</t>
+          <t>555659</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>620159</t>
+          <t>620523</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,29%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>224628</t>
+          <t>226469</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>271355</t>
+          <t>273004</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>169347</t>
+          <t>166440</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>212029</t>
+          <t>212356</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>409133</t>
+          <t>408769</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>474615</t>
+          <t>473633</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,02%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>117920</t>
+          <t>120680</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155539</t>
+          <t>154871</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>161382</t>
+          <t>160706</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>198160</t>
+          <t>198287</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>291242</t>
+          <t>289522</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>344177</t>
+          <t>340855</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,25%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>168507</t>
+          <t>169175</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>206126</t>
+          <t>203366</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142860</t>
+          <t>142733</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>179638</t>
+          <t>180314</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>320889</t>
+          <t>324211</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>373824</t>
+          <t>375544</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,47%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>120591</t>
+          <t>121884</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>159332</t>
+          <t>159807</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>178654</t>
+          <t>173742</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>217556</t>
+          <t>215080</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>308753</t>
+          <t>310028</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>365954</t>
+          <t>367611</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>48,18%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>214650</t>
+          <t>214175</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>253391</t>
+          <t>252098</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>171395</t>
+          <t>173871</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>210297</t>
+          <t>215209</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>396979</t>
+          <t>395322</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>454180</t>
+          <t>452905</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,36%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78960</t>
+          <t>79579</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110530</t>
+          <t>109577</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>112510</t>
+          <t>112226</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142761</t>
+          <t>142382</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>200845</t>
+          <t>199343</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>243878</t>
+          <t>242237</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,05%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>102088</t>
+          <t>103041</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>133658</t>
+          <t>133039</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76830</t>
+          <t>77209</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>107081</t>
+          <t>107365</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>188331</t>
+          <t>189972</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>231364</t>
+          <t>232866</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,88%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>112800</t>
+          <t>113605</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>146889</t>
+          <t>147973</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>139741</t>
+          <t>137923</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>173813</t>
+          <t>172074</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>261840</t>
+          <t>260963</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>309788</t>
+          <t>310745</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>56,09%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>127092</t>
+          <t>126008</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>161181</t>
+          <t>160376</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>106218</t>
+          <t>107957</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>140290</t>
+          <t>142108</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>244224</t>
+          <t>243267</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>292172</t>
+          <t>293049</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,9%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>248911</t>
+          <t>248533</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>303875</t>
+          <t>303419</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>343014</t>
+          <t>341693</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>395444</t>
+          <t>394306</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>607412</t>
+          <t>608354</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>681297</t>
+          <t>678125</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>49,99%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>358913</t>
+          <t>359369</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>413877</t>
+          <t>414255</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>298409</t>
+          <t>299547</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>350839</t>
+          <t>352160</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>675344</t>
+          <t>678516</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>749229</t>
+          <t>748287</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,16%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>294183</t>
+          <t>296042</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>352342</t>
+          <t>355595</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>378048</t>
+          <t>381322</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>437205</t>
+          <t>443034</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>691057</t>
+          <t>691260</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>780360</t>
+          <t>770543</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,07%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>426756</t>
+          <t>423503</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>484915</t>
+          <t>483056</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>386648</t>
+          <t>380819</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>445805</t>
+          <t>442531</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>822591</t>
+          <t>832408</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>911894</t>
+          <t>911691</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>56,88%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1454404</t>
+          <t>1445018</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1573064</t>
+          <t>1567650</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1874277</t>
+          <t>1876130</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1994639</t>
+          <t>1990743</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3351809</t>
+          <t>3363111</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3525395</t>
+          <t>3526124</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,48%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1853715</t>
+          <t>1859129</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1972375</t>
+          <t>1981761</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1563670</t>
+          <t>1567566</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1684032</t>
+          <t>1682179</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3459693</t>
+          <t>3458964</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3633279</t>
+          <t>3621977</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>51,85%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>117372</t>
+          <t>115554</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>152678</t>
+          <t>151734</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>140153</t>
+          <t>139253</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>174011</t>
+          <t>174077</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>263786</t>
+          <t>266300</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>316316</t>
+          <t>314612</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,01%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>141083</t>
+          <t>142027</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>176389</t>
+          <t>178207</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>114692</t>
+          <t>114626</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>148550</t>
+          <t>149450</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>266148</t>
+          <t>267852</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>318678</t>
+          <t>316164</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,28%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>204083</t>
+          <t>205105</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>251240</t>
+          <t>250265</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>256773</t>
+          <t>257301</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>300761</t>
+          <t>301015</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>472117</t>
+          <t>473384</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>538575</t>
+          <t>541293</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,78%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>251335</t>
+          <t>252310</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>298492</t>
+          <t>297470</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>222323</t>
+          <t>222069</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>266311</t>
+          <t>265783</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>487084</t>
+          <t>484366</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>553542</t>
+          <t>552275</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,85%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80965</t>
+          <t>81777</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111402</t>
+          <t>112595</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97332</t>
+          <t>96019</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>131807</t>
+          <t>131205</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>184480</t>
+          <t>185901</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>231817</t>
+          <t>235231</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,92%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>207163</t>
+          <t>205970</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>237600</t>
+          <t>236788</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>204502</t>
+          <t>205104</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>238977</t>
+          <t>240290</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>423057</t>
+          <t>419643</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>470394</t>
+          <t>468973</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,61%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>187181</t>
+          <t>188022</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>227146</t>
+          <t>225931</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>225413</t>
+          <t>228289</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>266683</t>
+          <t>266432</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>424298</t>
+          <t>424864</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>479978</t>
+          <t>481169</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,54%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>142818</t>
+          <t>144033</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>182783</t>
+          <t>181942</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>120600</t>
+          <t>120851</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>161870</t>
+          <t>158994</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>277269</t>
+          <t>276078</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>332949</t>
+          <t>332383</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>43,89%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52875</t>
+          <t>52943</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79877</t>
+          <t>79983</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71608</t>
+          <t>71200</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>101500</t>
+          <t>99866</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>132118</t>
+          <t>131973</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>170545</t>
+          <t>172151</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>40,05%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>131344</t>
+          <t>131238</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>158346</t>
+          <t>158278</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117087</t>
+          <t>118721</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>146979</t>
+          <t>147387</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>259263</t>
+          <t>257657</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>297690</t>
+          <t>297835</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,29%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>76717</t>
+          <t>76595</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>107672</t>
+          <t>107286</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>108264</t>
+          <t>108400</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>140916</t>
+          <t>140980</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>193816</t>
+          <t>193754</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>241443</t>
+          <t>238582</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,49%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>155451</t>
+          <t>155837</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>186406</t>
+          <t>186528</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>132199</t>
+          <t>132135</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>164851</t>
+          <t>164715</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>294795</t>
+          <t>297656</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>342422</t>
+          <t>342484</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,87%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>227260</t>
+          <t>224230</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>276781</t>
+          <t>275959</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>314631</t>
+          <t>314269</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>365758</t>
+          <t>366146</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>559045</t>
+          <t>555550</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>635211</t>
+          <t>628076</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>46,6%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>379777</t>
+          <t>380599</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>429298</t>
+          <t>432328</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>325536</t>
+          <t>325148</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>376663</t>
+          <t>377025</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>712641</t>
+          <t>719776</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>788807</t>
+          <t>792302</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,78%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>225099</t>
+          <t>221225</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>275246</t>
+          <t>275046</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>322558</t>
+          <t>318517</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>380309</t>
+          <t>378821</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>558082</t>
+          <t>562662</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>639015</t>
+          <t>639052</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>503337</t>
+          <t>503537</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>553484</t>
+          <t>557358</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>445858</t>
+          <t>447346</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>503609</t>
+          <t>507650</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>965735</t>
+          <t>965698</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1046668</t>
+          <t>1042088</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>64,94%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1265887</t>
+          <t>1270190</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1383208</t>
+          <t>1384774</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1638475</t>
+          <t>1632684</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1758059</t>
+          <t>1752258</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2927561</t>
+          <t>2928023</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3102177</t>
+          <t>3099135</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,66%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2011142</t>
+          <t>2009576</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2128463</t>
+          <t>2124160</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1786483</t>
+          <t>1792284</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1906067</t>
+          <t>1911858</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3836715</t>
+          <t>3839757</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4011331</t>
+          <t>4010869</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>57,8%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>189437</t>
+          <t>201403</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>165620</t>
+          <t>182589</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>209758</t>
+          <t>219357</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>231287</t>
+          <t>249100</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>218191</t>
+          <t>235124</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>242760</t>
+          <t>260487</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>420723</t>
+          <t>450503</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>389221</t>
+          <t>427369</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>444879</t>
+          <t>472289</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,39%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>122006</t>
+          <t>117442</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101685</t>
+          <t>99488</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>145823</t>
+          <t>136256</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>58348</t>
+          <t>66961</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46875</t>
+          <t>55574</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71444</t>
+          <t>80937</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>180354</t>
+          <t>184403</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>156198</t>
+          <t>162617</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>211856</t>
+          <t>207537</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>232177</t>
+          <t>238211</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>202796</t>
+          <t>210339</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>259856</t>
+          <t>266545</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>287324</t>
+          <t>301924</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>268097</t>
+          <t>280500</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>305853</t>
+          <t>324006</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>519501</t>
+          <t>540134</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>480363</t>
+          <t>500907</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>551589</t>
+          <t>576821</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,67%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>285342</t>
+          <t>291447</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>257663</t>
+          <t>263113</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>314723</t>
+          <t>319319</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>226253</t>
+          <t>243108</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>207724</t>
+          <t>221026</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>245480</t>
+          <t>264532</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>511595</t>
+          <t>534555</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>479507</t>
+          <t>497868</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>550733</t>
+          <t>573782</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,39%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517519</t>
+          <t>529658</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517519</t>
+          <t>529658</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517519</t>
+          <t>529658</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513577</t>
+          <t>545032</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513577</t>
+          <t>545032</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513577</t>
+          <t>545032</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031096</t>
+          <t>1074689</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031096</t>
+          <t>1074689</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031096</t>
+          <t>1074689</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>164971</t>
+          <t>165679</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>146549</t>
+          <t>149743</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>182277</t>
+          <t>184708</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,22 +11418,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>178911</t>
+          <t>182010</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>162150</t>
+          <t>165588</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>195687</t>
+          <t>197152</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,17 +11453,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>343882</t>
+          <t>347690</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>318851</t>
+          <t>324879</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>367790</t>
+          <t>370096</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,61%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>149106</t>
+          <t>148392</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>131800</t>
+          <t>129363</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>167528</t>
+          <t>164328</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,27 +11531,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>165194</t>
+          <t>169408</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148418</t>
+          <t>154266</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>181955</t>
+          <t>185830</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -11566,17 +11566,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>314300</t>
+          <t>317800</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>290392</t>
+          <t>295394</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>339331</t>
+          <t>340611</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,18%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>314077</t>
+          <t>314071</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>314077</t>
+          <t>314071</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>314077</t>
+          <t>314071</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>344105</t>
+          <t>351418</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>344105</t>
+          <t>351418</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>344105</t>
+          <t>351418</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>658182</t>
+          <t>665490</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>658182</t>
+          <t>665490</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>658182</t>
+          <t>665490</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>150201</t>
+          <t>167904</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>128819</t>
+          <t>142360</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>171910</t>
+          <t>193302</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>198363</t>
+          <t>222985</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>117621</t>
+          <t>201547</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>251654</t>
+          <t>243034</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>348564</t>
+          <t>390889</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>241723</t>
+          <t>355607</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>400160</t>
+          <t>423329</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>54,1%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>155983</t>
+          <t>198237</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>134274</t>
+          <t>172839</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177365</t>
+          <t>223781</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>272116</t>
+          <t>193431</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>218825</t>
+          <t>173382</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>352858</t>
+          <t>214869</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>428099</t>
+          <t>391668</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>376503</t>
+          <t>359228</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>534940</t>
+          <t>426950</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>54,56%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>306184</t>
+          <t>366141</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>306184</t>
+          <t>366141</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>306184</t>
+          <t>366141</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>470479</t>
+          <t>416416</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>470479</t>
+          <t>416416</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>470479</t>
+          <t>416416</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>776663</t>
+          <t>782557</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>776663</t>
+          <t>782557</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>776663</t>
+          <t>782557</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>74067</t>
+          <t>82459</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64104</t>
+          <t>70271</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85435</t>
+          <t>94313</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>109185</t>
+          <t>115290</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>98774</t>
+          <t>104595</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119330</t>
+          <t>126175</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>183251</t>
+          <t>197750</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>168884</t>
+          <t>180491</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>197946</t>
+          <t>214874</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>104172</t>
+          <t>122713</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92804</t>
+          <t>110859</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114135</t>
+          <t>134901</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>97462</t>
+          <t>109847</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87317</t>
+          <t>98962</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>107873</t>
+          <t>120542</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>201635</t>
+          <t>232559</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>186940</t>
+          <t>215435</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>216002</t>
+          <t>249818</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>58,06%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178239</t>
+          <t>205172</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178239</t>
+          <t>205172</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178239</t>
+          <t>205172</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>206647</t>
+          <t>225137</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>206647</t>
+          <t>225137</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>206647</t>
+          <t>225137</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>384886</t>
+          <t>430309</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>384886</t>
+          <t>430309</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>384886</t>
+          <t>430309</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>147654</t>
+          <t>147551</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>133176</t>
+          <t>134025</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>163608</t>
+          <t>162865</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>159462</t>
+          <t>164348</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>147027</t>
+          <t>150481</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>172960</t>
+          <t>177517</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>307116</t>
+          <t>311899</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>286837</t>
+          <t>291581</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>326090</t>
+          <t>332545</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,28%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>121510</t>
+          <t>122679</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>105556</t>
+          <t>107365</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>135988</t>
+          <t>136205</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>97594</t>
+          <t>99402</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>84096</t>
+          <t>86233</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>110029</t>
+          <t>113269</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>219104</t>
+          <t>222081</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>200130</t>
+          <t>201435</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>239383</t>
+          <t>242399</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,39%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269164</t>
+          <t>270230</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269164</t>
+          <t>270230</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269164</t>
+          <t>270230</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526220</t>
+          <t>533980</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526220</t>
+          <t>533980</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526220</t>
+          <t>533980</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>297941</t>
+          <t>351330</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>267566</t>
+          <t>320216</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>327210</t>
+          <t>382601</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>536702</t>
+          <t>399966</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>429115</t>
+          <t>372221</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>698925</t>
+          <t>423944</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>834644</t>
+          <t>751297</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>716268</t>
+          <t>711239</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1101041</t>
+          <t>791738</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>53,35%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>321960</t>
+          <t>363290</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>292691</t>
+          <t>332019</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>352335</t>
+          <t>394404</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>310162</t>
+          <t>369396</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>147939</t>
+          <t>345418</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>417749</t>
+          <t>397141</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>632121</t>
+          <t>732685</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>365724</t>
+          <t>692244</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>750497</t>
+          <t>772743</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>52,07%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>619901</t>
+          <t>714620</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>619901</t>
+          <t>714620</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>619901</t>
+          <t>714620</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>846864</t>
+          <t>769362</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>846864</t>
+          <t>769362</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>846864</t>
+          <t>769362</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1466765</t>
+          <t>1483982</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1466765</t>
+          <t>1483982</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1466765</t>
+          <t>1483982</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>458464</t>
+          <t>244018</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>281912</t>
+          <t>220537</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>712108</t>
+          <t>271922</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>292559</t>
+          <t>331352</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>268889</t>
+          <t>304572</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>314109</t>
+          <t>356640</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>751023</t>
+          <t>575370</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>584079</t>
+          <t>540049</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1123850</t>
+          <t>614090</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>37,79%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>468720</t>
+          <t>552347</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>215076</t>
+          <t>524443</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>645272</t>
+          <t>575828</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>422682</t>
+          <t>497099</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>401132</t>
+          <t>471811</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>446352</t>
+          <t>523879</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>891402</t>
+          <t>1049446</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>518575</t>
+          <t>1010726</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1058346</t>
+          <t>1084767</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>66,76%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>927184</t>
+          <t>796365</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>927184</t>
+          <t>796365</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>927184</t>
+          <t>796365</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715241</t>
+          <t>828451</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715241</t>
+          <t>828451</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715241</t>
+          <t>828451</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1642425</t>
+          <t>1624816</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1642425</t>
+          <t>1624816</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1642425</t>
+          <t>1624816</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1714911</t>
+          <t>1598557</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1563703</t>
+          <t>1537537</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2095632</t>
+          <t>1660921</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1993792</t>
+          <t>1966976</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1855890</t>
+          <t>1917711</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2301980</t>
+          <t>2026014</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3708703</t>
+          <t>3565533</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3474211</t>
+          <t>3480317</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4180808</t>
+          <t>3649031</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>50,47%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1728800</t>
+          <t>1916546</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1348079</t>
+          <t>1854182</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1880008</t>
+          <t>1977566</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1649811</t>
+          <t>1748651</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1341623</t>
+          <t>1689613</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1787713</t>
+          <t>1797916</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3378611</t>
+          <t>3665197</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2906506</t>
+          <t>3581699</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3613103</t>
+          <t>3750413</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,87%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3443711</t>
+          <t>3515103</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3443711</t>
+          <t>3515103</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3443711</t>
+          <t>3515103</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3643603</t>
+          <t>3715627</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3643603</t>
+          <t>3715627</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3643603</t>
+          <t>3715627</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7087314</t>
+          <t>7230730</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7087314</t>
+          <t>7230730</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7087314</t>
+          <t>7230730</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
